--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>1416.95</v>
+        <v>1400</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1381.25</v>
+        <v>1370.25</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>3004.7</v>
+        <v>2943.1</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1410</v>
+        <v>1385.7</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1386.35</v>
+        <v>1388.25</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1488.1</v>
+        <v>1409.1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1455.35</v>
+        <v>1386</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1478.4</v>
+        <v>1394.7</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1479.25</v>
+        <v>1405.45</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1459.65</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="4">
@@ -545,22 +545,22 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>52420</v>
+        <v>52440</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>51222.35</v>
+        <v>51704</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>52361.4</v>
+        <v>52034.2</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>52310.4</v>
+        <v>51954.4</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>51250.05</v>
+        <v>52205</v>
       </c>
     </row>
     <row r="5">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>105.5</v>
+        <v>104.24</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>101.01</v>
+        <v>102.18</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>105</v>
+        <v>103.01</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>105.12</v>
+        <v>103.32</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>589</v>
+        <v>839</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>101.09</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="6">
@@ -595,22 +595,22 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>882.5</v>
+        <v>828</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>851.1</v>
+        <v>813.7</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>877</v>
+        <v>814.8</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>878.4</v>
+        <v>825.3</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>853.05</v>
+        <v>825.05</v>
       </c>
     </row>
     <row r="7">
@@ -620,22 +620,22 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>759.5</v>
+        <v>689.1</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>727.45</v>
+        <v>679.5</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>756.65</v>
+        <v>684.35</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>756.9</v>
+        <v>690.55</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>727.5</v>
+        <v>685.25</v>
       </c>
     </row>
     <row r="8">
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1269.3</v>
+        <v>1317.25</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1229.55</v>
+        <v>1289.5</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1268.95</v>
+        <v>1297.15</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1266.85</v>
+        <v>1301.55</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>287</v>
+        <v>155</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1231.95</v>
+        <v>1315.25</v>
       </c>
     </row>
     <row r="9">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>975</v>
+        <v>931.55</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>925.4</v>
+        <v>909.9</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>968.75</v>
+        <v>920</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>968.35</v>
+        <v>925.8</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>925.9</v>
+        <v>923.3</v>
       </c>
     </row>
     <row r="10">
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>24996.75</v>
+        <v>24450</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>24640.2</v>
+        <v>24322</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>24965.55</v>
+        <v>24405.95</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>24949.15</v>
+        <v>24388.3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>24656.5</v>
+        <v>24431.95</v>
       </c>
     </row>
     <row r="11">
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>2744.95</v>
+        <v>1340.4</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2692</v>
+        <v>1324.55</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2727</v>
+        <v>1331</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2728.6</v>
+        <v>1338.75</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>120</v>
+        <v>440</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>2693.2</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="12">
@@ -745,22 +745,22 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>826.7</v>
+        <v>828.4</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>805.05</v>
+        <v>814.4</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>823.4</v>
+        <v>821</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>824.3</v>
+        <v>826.15</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>309</v>
+        <v>214</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>806.7</v>
+        <v>822.95</v>
       </c>
     </row>
     <row r="13">
@@ -770,22 +770,22 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1102.4</v>
+        <v>1012.25</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1076.7</v>
+        <v>997.75</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1097.45</v>
+        <v>998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>1098.3</v>
+        <v>1006.75</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>28</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1080.6</v>
+        <v>1011.45</v>
       </c>
     </row>
     <row r="14">
@@ -795,22 +795,22 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>920.5</v>
+        <v>840.5</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>891.6</v>
+        <v>831.35</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>913.8</v>
+        <v>835.3</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>913.55</v>
+        <v>839.8</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>163</v>
+        <v>244</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>892.65</v>
+        <v>835.3</v>
       </c>
     </row>
     <row r="15">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>156.9</v>
+        <v>149.77</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>151.62</v>
+        <v>147.97</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>156.01</v>
+        <v>147.99</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>156.09</v>
+        <v>149.58</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>642</v>
+        <v>949</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>151.7</v>
+        <v>148.88</v>
       </c>
     </row>
     <row r="16">
@@ -845,22 +845,22 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>4152.95</v>
+        <v>4014.45</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4111.65</v>
+        <v>3953.05</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>4140</v>
+        <v>3976.95</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>4136.3</v>
+        <v>3993.85</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>4129.05</v>
+        <v>4011.25</v>
       </c>
     </row>
     <row r="17">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>3429.65</v>
+        <v>3281.95</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3301.75</v>
+        <v>3248.5</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>3408.7</v>
+        <v>3271.7</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>3397.5</v>
+        <v>3285</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>3340.55</v>
+        <v>3269</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -27,24 +27,27 @@
     <t>CLOSE</t>
   </si>
   <si>
+    <t>VOL</t>
+  </si>
+  <si>
+    <t>9:25 CLOSE</t>
+  </si>
+  <si>
+    <t>BN</t>
+  </si>
+  <si>
+    <t>NIFTY</t>
+  </si>
+  <si>
     <t>LTP</t>
   </si>
   <si>
-    <t>VOL</t>
-  </si>
-  <si>
-    <t>9:25 CLOSE</t>
-  </si>
-  <si>
     <t>ADANI</t>
   </si>
   <si>
     <t>AURO</t>
   </si>
   <si>
-    <t>BN</t>
-  </si>
-  <si>
     <t>CANBK</t>
   </si>
   <si>
@@ -58,9 +61,6 @@
   </si>
   <si>
     <t>JIND</t>
-  </si>
-  <si>
-    <t>NIFTY</t>
   </si>
   <si>
     <t>REL</t>
@@ -471,36 +471,60 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="B2" s="1">
+        <v>52486.45</v>
+      </c>
+      <c r="C2" s="2">
+        <v>52035.45</v>
+      </c>
+      <c r="D2" s="1">
+        <v>52345</v>
+      </c>
+      <c r="E2" s="1">
+        <v>52364.45</v>
+      </c>
+      <c r="F2" s="1">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1">
+        <v>52372.35</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>24367.95</v>
+      </c>
+      <c r="C3" s="2">
+        <v>24112</v>
+      </c>
+      <c r="D3" s="1">
+        <v>24318.25</v>
+      </c>
+      <c r="E3" s="1">
+        <v>24304.15</v>
+      </c>
+      <c r="F3" s="1">
+        <v>65</v>
+      </c>
+      <c r="G3" s="1">
+        <v>24130</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -524,18 +548,18 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
@@ -546,7 +570,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
@@ -557,7 +581,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="2"/>
@@ -568,7 +592,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
@@ -579,7 +603,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
@@ -590,7 +614,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
@@ -601,7 +625,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
@@ -612,7 +636,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
@@ -623,7 +647,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>53900</v>
+        <v>51483.85</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>53465</v>
+        <v>51152.8</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>53535.85</v>
+        <v>51300.3</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>53531</v>
+        <v>51303.15</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>53737.85</v>
+        <v>51201.3</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>53900</v>
+        <v>23901.8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>53465</v>
+        <v>23664.1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>24698.6</v>
+        <v>23768</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>24694.6</v>
+        <v>23769.75</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>53737.85</v>
+        <v>23791</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>51483.85</v>
+        <v>48977.95</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>51152.8</v>
+        <v>48425</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>51300.3</v>
+        <v>48711.95</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>51303.15</v>
+        <v>48685.65</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>51201.3</v>
+        <v>48940</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>23901.8</v>
+        <v>23343.4</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>23664.1</v>
+        <v>23150.1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>23768</v>
+        <v>23261.75</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>23769.75</v>
+        <v>23267.2</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>23791</v>
+        <v>23260.4</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>48977.95</v>
+        <v>49995</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>48425</v>
+        <v>49364.5</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>48711.95</v>
+        <v>49882.05</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>48685.65</v>
+        <v>49862</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>48940</v>
+        <v>49490.2</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>23343.4</v>
+        <v>23644</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>23150.1</v>
+        <v>23431</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>23261.75</v>
+        <v>23639</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>23267.2</v>
+        <v>23620.2</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>23260.4</v>
+        <v>23456</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>49995</v>
+        <v>48150</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>49364.5</v>
+        <v>47769.2</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>49882.05</v>
+        <v>48060</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>49862</v>
+        <v>47999.5</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>49490.2</v>
+        <v>47844.15</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>23644</v>
+        <v>22592.05</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>23431</v>
+        <v>22366.65</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>23639</v>
+        <v>22589.95</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>23620.2</v>
+        <v>22564.3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>23456</v>
+        <v>22384.25</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>48150</v>
+        <v>50670</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>47769.2</v>
+        <v>50040.3</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>48060</v>
+        <v>50485</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>47999.5</v>
+        <v>50468.6</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>47844.15</v>
+        <v>50616</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>22592.05</v>
+        <v>22533.25</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>22366.65</v>
+        <v>22405.05</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>22589.95</v>
+        <v>22504</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>22564.3</v>
+        <v>22479.65</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>22384.25</v>
+        <v>22492.55</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>50670</v>
+        <v>55532.4</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>50040.3</v>
+        <v>55305</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>50485</v>
+        <v>55516.2</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>50468.6</v>
+        <v>55503.2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>50616</v>
+        <v>55407.8</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>22533.25</v>
+        <v>25139</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>22405.05</v>
+        <v>25006</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>22504</v>
+        <v>25081.9</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>22479.65</v>
+        <v>25078.7</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>22492.55</v>
+        <v>25052.7</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>55532.4</v>
+        <v>55559.4</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>55305</v>
+        <v>55020</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>55516.2</v>
+        <v>55519.8</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>55503.2</v>
+        <v>55495.6</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>55407.8</v>
+        <v>55099.8</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>25139</v>
+        <v>24961.7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>25006</v>
+        <v>24710.9</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>25081.9</v>
+        <v>24890</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>25078.7</v>
+        <v>24879.9</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>25052.7</v>
+        <v>24741.8</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>55559.4</v>
+        <v>54428.4</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>55020</v>
+        <v>53936.8</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>55519.8</v>
+        <v>54391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>55495.6</v>
+        <v>54373.6</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>55099.8</v>
+        <v>53967.8</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>24961.7</v>
+        <v>24837</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>24710.9</v>
+        <v>24651</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>24890</v>
+        <v>24820</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>24879.9</v>
+        <v>24813.1</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>24741.8</v>
+        <v>24664.4</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>54428.4</v>
+        <v>54654</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>53936.8</v>
+        <v>54211.8</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>54391</v>
+        <v>54324.6</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>54373.6</v>
+        <v>54293</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>53967.8</v>
+        <v>54514.4</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>24837</v>
+        <v>25034</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>24651</v>
+        <v>24809.7</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>24820</v>
+        <v>24836</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>24813.1</v>
+        <v>24827.5</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>24664.4</v>
+        <v>24974.4</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>54654</v>
+        <v>56375.8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>54211.8</v>
+        <v>55960.2</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>54324.6</v>
+        <v>56300</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>54293</v>
+        <v>56297.8</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>54514.4</v>
+        <v>56058.2</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>25034</v>
+        <v>25199.1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>24809.7</v>
+        <v>24973.2</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>24836</v>
+        <v>25181.1</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>24827.5</v>
+        <v>25185.4</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>24974.4</v>
+        <v>25012.6</v>
       </c>
     </row>
   </sheetData>

--- a/fo high low.xlsx
+++ b/fo high low.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>56375.8</v>
+        <v>59372.4</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>55960.2</v>
+        <v>58370</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>56300</v>
+        <v>58470.2</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>56297.8</v>
+        <v>58522.8</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>56058.2</v>
+        <v>59340</v>
       </c>
     </row>
     <row r="3">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>25199.1</v>
+        <v>25369.9</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>24973.2</v>
+        <v>25045.7</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>25181.1</v>
+        <v>25080</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>25185.4</v>
+        <v>25079.8</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>25012.6</v>
+        <v>25351</v>
       </c>
     </row>
   </sheetData>
